--- a/planning.xlsx
+++ b/planning.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="132" windowWidth="22932" windowHeight="9240"/>
+    <workbookView xWindow="96" yWindow="132" windowWidth="22932" windowHeight="9240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>amount</t>
   </si>
@@ -31,6 +31,21 @@
   </si>
   <si>
     <t>compound</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Z</t>
   </si>
 </sst>
 </file>
@@ -517,9 +532,55 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1">
+        <f>CODE(A1)</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <f t="shared" ref="B2:B5" si="0">CODE(A2)</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
